--- a/diansai/器件清单.xlsx
+++ b/diansai/器件清单.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\my_code\my_code\diansai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64BAF2CE-A8E6-4B8E-9F38-48255118899B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5AEFDAC-609E-433C-8E67-EE7EC6435B56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{81367D8F-0917-4FDC-802A-4AEAC8A440C9}"/>
+    <workbookView xWindow="5590" yWindow="1590" windowWidth="19200" windowHeight="11720" xr2:uid="{81367D8F-0917-4FDC-802A-4AEAC8A440C9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="16">
   <si>
     <t>价格</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -44,10 +44,6 @@
   </si>
   <si>
     <t>器件清单（暂定）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>逐飞蓝牙模块</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -483,7 +479,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -496,7 +492,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4">
         <f>99*2</f>
@@ -519,17 +515,9 @@
         <v>59.9</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7">
-        <v>85</v>
-      </c>
-    </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8">
         <v>38.9</v>
@@ -537,21 +525,21 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9">
         <f>SUM(B3,B4,B5,B6,B7,B8)</f>
-        <v>659.8</v>
+        <v>574.79999999999995</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B11">
         <v>219</v>
@@ -559,7 +547,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B12">
         <v>374</v>
@@ -567,7 +555,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B13">
         <f>99*2</f>
@@ -576,7 +564,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B14">
         <v>315</v>
@@ -584,7 +572,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B15">
         <v>96</v>
@@ -596,7 +584,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B16">
         <v>40</v>
@@ -604,11 +592,11 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B17">
         <f>SUM(B11:B16,B9)</f>
-        <v>1901.8</v>
+        <v>1816.8</v>
       </c>
     </row>
   </sheetData>
